--- a/data/trans_dic/P6903-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P6903-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas</t>
+          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas (tasa de respuesta: 99,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,85; 52,15</t>
+          <t>22,81; 52,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,99; 75,46</t>
+          <t>13,21; 76,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,58; 69,85</t>
+          <t>23,4; 69,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,55; 53,4</t>
+          <t>14,5; 54,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,16; 72,2</t>
+          <t>11,35; 79,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,3; 83,19</t>
+          <t>25,08; 78,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,48; 74,53</t>
+          <t>11,47; 75,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,64; 46,73</t>
+          <t>24,41; 47,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,86; 65,11</t>
+          <t>21,73; 67,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,01; 64,25</t>
+          <t>28,53; 64,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,76; 67,9</t>
+          <t>13,87; 66,87</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,54; 42,76</t>
+          <t>26,66; 43,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,51; 37,28</t>
+          <t>17,32; 38,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,45; 48,93</t>
+          <t>25,71; 48,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,18; 60,43</t>
+          <t>25,81; 59,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,87; 37,65</t>
+          <t>18,04; 38,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,16; 47,68</t>
+          <t>25,53; 49,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,83; 47,47</t>
+          <t>20,23; 46,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,25; 56,96</t>
+          <t>28,22; 57,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,04; 39,16</t>
+          <t>25,99; 38,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,3; 39,34</t>
+          <t>22,79; 39,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,07; 44,33</t>
+          <t>27,09; 45,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,4; 54,09</t>
+          <t>31,3; 54,34</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,27; 45,33</t>
+          <t>28,04; 45,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,0; 38,11</t>
+          <t>19,31; 37,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,36; 46,36</t>
+          <t>27,82; 46,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,15; 38,22</t>
+          <t>19,34; 37,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,88; 43,69</t>
+          <t>20,93; 42,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,42; 49,45</t>
+          <t>25,78; 48,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,08; 55,26</t>
+          <t>32,26; 55,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,86; 48,42</t>
+          <t>29,03; 47,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,64; 42,32</t>
+          <t>27,27; 41,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,72; 39,4</t>
+          <t>24,9; 39,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,65; 47,36</t>
+          <t>32,74; 47,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,68; 38,8</t>
+          <t>26,24; 39,61</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,99; 36,06</t>
+          <t>18,69; 36,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,62; 28,54</t>
+          <t>11,64; 28,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,14; 51,06</t>
+          <t>29,56; 50,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,96; 46,78</t>
+          <t>27,77; 46,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,68; 56,31</t>
+          <t>24,64; 54,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,22; 41,88</t>
+          <t>10,74; 37,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,75; 54,17</t>
+          <t>28,35; 56,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,05; 49,61</t>
+          <t>17,64; 49,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,38; 37,69</t>
+          <t>22,27; 37,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,31; 29,59</t>
+          <t>14,12; 29,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32,8; 50,27</t>
+          <t>32,56; 49,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,73; 45,33</t>
+          <t>24,56; 44,69</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,27; 29,84</t>
+          <t>8,24; 29,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,84; 25,0</t>
+          <t>4,82; 25,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,38; 57,79</t>
+          <t>29,33; 58,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,62; 45,12</t>
+          <t>23,58; 44,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,14; 57,81</t>
+          <t>7,34; 57,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,94; 65,12</t>
+          <t>23,99; 63,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,79; 63,78</t>
+          <t>27,01; 65,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>35,08; 55,13</t>
+          <t>35,14; 54,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,01; 31,5</t>
+          <t>11,25; 31,55</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,0; 35,37</t>
+          <t>14,33; 36,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31,97; 55,43</t>
+          <t>33,0; 56,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,33; 45,88</t>
+          <t>31,28; 46,28</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,89</t>
+          <t>0,0; 80,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,93</t>
+          <t>0,0; 50,62</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>27,29; 36,11</t>
+          <t>27,44; 36,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,21; 28,57</t>
+          <t>19,51; 28,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33,68; 44,25</t>
+          <t>33,63; 44,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28,69; 40,75</t>
+          <t>28,56; 39,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>25,09; 37,85</t>
+          <t>24,95; 36,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,46; 41,47</t>
+          <t>28,64; 41,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,45; 48,95</t>
+          <t>34,33; 47,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>28,29; 45,54</t>
+          <t>28,62; 45,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27,76; 35,01</t>
+          <t>27,74; 35,08</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24,5; 32,35</t>
+          <t>24,0; 32,52</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35,71; 44,29</t>
+          <t>35,78; 44,41</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>31,06; 40,98</t>
+          <t>30,31; 40,89</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas</t>
+          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas (tasa de respuesta: 99,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10551; 24076</t>
+          <t>10531; 24112</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1342; 7793</t>
+          <t>1365; 7856</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4043; 11980</t>
+          <t>4013; 11974</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2088,42 +2088,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2095; 10604</t>
+          <t>2879; 10744</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1122; 7261</t>
+          <t>1142; 7983</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2945; 9686</t>
+          <t>2920; 9092</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1609; 11436</t>
+          <t>1759; 11517</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16271; 30857</t>
+          <t>16120; 31458</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4660; 13271</t>
+          <t>4428; 13762</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8066; 18499</t>
+          <t>8215; 18709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2936; 14484</t>
+          <t>2958; 14266</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37764; 60849</t>
+          <t>37940; 61199</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14926; 31776</t>
+          <t>14765; 32573</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21574; 39915</t>
+          <t>20969; 39175</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14878; 35699</t>
+          <t>15249; 35159</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14163; 29844</t>
+          <t>14305; 30374</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16216; 32001</t>
+          <t>17135; 33515</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9640; 21975</t>
+          <t>9367; 21385</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13612; 28449</t>
+          <t>14093; 28624</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57687; 86776</t>
+          <t>57574; 86257</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35499; 59939</t>
+          <t>34720; 59900</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35897; 56685</t>
+          <t>34641; 58169</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34234; 58970</t>
+          <t>34124; 59243</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35624; 57134</t>
+          <t>35337; 57580</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19573; 37304</t>
+          <t>18901; 36683</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32085; 52447</t>
+          <t>31471; 52214</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18292; 36510</t>
+          <t>18472; 36281</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14623; 30604</t>
+          <t>14657; 29860</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18459; 35915</t>
+          <t>18726; 35560</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23638; 39489</t>
+          <t>23053; 39679</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21807; 36579</t>
+          <t>21931; 36180</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56154; 82984</t>
+          <t>53462; 80792</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42149; 67183</t>
+          <t>42461; 68048</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60262; 87411</t>
+          <t>60430; 87109</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43930; 66373</t>
+          <t>44899; 67759</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21098; 40070</t>
+          <t>20769; 40384</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10340; 25408</t>
+          <t>10359; 25488</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26638; 46687</t>
+          <t>27023; 46358</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28778; 49944</t>
+          <t>29645; 49398</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9140; 20857</t>
+          <t>9126; 20292</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5327; 16877</t>
+          <t>4328; 15278</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16133; 30391</t>
+          <t>15909; 31532</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24760; 76533</t>
+          <t>27211; 76648</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33160; 55832</t>
+          <t>32991; 55732</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18505; 38268</t>
+          <t>18260; 38016</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>48389; 74159</t>
+          <t>48042; 72779</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>61951; 118316</t>
+          <t>64103; 116658</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3795; 13692</t>
+          <t>3780; 13684</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2025; 10457</t>
+          <t>2015; 10546</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13175; 25919</t>
+          <t>13154; 26412</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15725; 30038</t>
+          <t>15701; 29923</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>994; 8040</t>
+          <t>1021; 7988</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5393; 16007</t>
+          <t>5898; 15691</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7944; 19643</t>
+          <t>8318; 20257</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19470; 30603</t>
+          <t>19505; 30100</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6581; 18835</t>
+          <t>6725; 18865</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9301; 23488</t>
+          <t>9518; 23935</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24187; 41928</t>
+          <t>24960; 42669</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>37031; 56016</t>
+          <t>38190; 56502</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1070</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 894</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2415</t>
+          <t>0; 2358</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 1070</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3206</t>
+          <t>0; 2954</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 633</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 633</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>128890; 170546</t>
+          <t>129613; 170683</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>62308; 92651</t>
+          <t>63279; 93865</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>117870; 154859</t>
+          <t>117715; 156230</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>96638; 137275</t>
+          <t>96204; 133498</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>55237; 83314</t>
+          <t>54919; 81376</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>61107; 89027</t>
+          <t>61476; 88549</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>76669; 105873</t>
+          <t>74264; 103788</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>99999; 160985</t>
+          <t>101182; 160700</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>192224; 242444</t>
+          <t>192104; 242897</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>132031; 174382</t>
+          <t>129351; 175264</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>202214; 250839</t>
+          <t>202638; 251475</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>214441; 282906</t>
+          <t>209245; 282302</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6903-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P6903-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>47,84%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,81; 52,22</t>
+          <t>24,11; 52,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,21; 76,08</t>
+          <t>13,87; 76,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,4; 69,82</t>
+          <t>19,05; 68,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,5; 54,1</t>
+          <t>14,13; 50,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,35; 79,39</t>
+          <t>10,07; 79,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,08; 78,09</t>
+          <t>24,92; 77,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,47; 75,06</t>
+          <t>12,68; 77,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,41; 47,64</t>
+          <t>23,69; 48,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,73; 67,51</t>
+          <t>21,37; 67,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,53; 64,97</t>
+          <t>25,85; 64,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,87; 66,87</t>
+          <t>21,7; 76,39</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>44,07%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,66; 43,01</t>
+          <t>26,5; 44,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,32; 38,21</t>
+          <t>16,82; 37,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,71; 48,03</t>
+          <t>25,7; 49,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,81; 59,52</t>
+          <t>29,82; 62,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,04; 38,31</t>
+          <t>17,03; 37,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,53; 49,94</t>
+          <t>23,56; 48,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,23; 46,2</t>
+          <t>21,09; 47,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,22; 57,31</t>
+          <t>27,7; 55,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,99; 38,93</t>
+          <t>25,62; 38,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,79; 39,32</t>
+          <t>22,98; 38,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,09; 45,49</t>
+          <t>27,82; 44,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,3; 54,34</t>
+          <t>33,0; 55,33</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,04; 45,69</t>
+          <t>27,02; 44,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,31; 37,48</t>
+          <t>19,52; 38,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,82; 46,16</t>
+          <t>27,38; 46,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,34; 37,98</t>
+          <t>18,62; 37,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,93; 42,63</t>
+          <t>21,42; 42,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,78; 48,96</t>
+          <t>25,67; 49,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,26; 55,53</t>
+          <t>31,65; 54,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,03; 47,89</t>
+          <t>28,8; 47,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,27; 41,21</t>
+          <t>27,38; 41,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,9; 39,91</t>
+          <t>24,8; 39,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,74; 47,19</t>
+          <t>32,92; 47,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,24; 39,61</t>
+          <t>25,69; 38,3</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>42,03%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,69; 36,35</t>
+          <t>18,43; 36,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,64; 28,63</t>
+          <t>12,05; 29,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,56; 50,7</t>
+          <t>29,13; 50,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,77; 46,27</t>
+          <t>29,81; 48,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,64; 54,79</t>
+          <t>24,57; 56,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,74; 37,91</t>
+          <t>12,68; 40,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,35; 56,2</t>
+          <t>28,35; 54,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,64; 49,69</t>
+          <t>38,09; 52,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,27; 37,62</t>
+          <t>22,08; 37,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,12; 29,4</t>
+          <t>14,58; 29,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32,56; 49,33</t>
+          <t>32,24; 49,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,56; 44,69</t>
+          <t>36,63; 48,1</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>39,75%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,24; 29,82</t>
+          <t>7,84; 30,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,82; 25,21</t>
+          <t>4,78; 25,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,33; 58,89</t>
+          <t>29,4; 60,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,58; 44,95</t>
+          <t>23,92; 45,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,34; 57,43</t>
+          <t>7,34; 57,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,99; 63,83</t>
+          <t>22,01; 64,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,01; 65,77</t>
+          <t>25,41; 64,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>35,14; 54,23</t>
+          <t>36,95; 56,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,25; 31,55</t>
+          <t>11,4; 31,48</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,33; 36,04</t>
+          <t>12,92; 35,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,0; 56,41</t>
+          <t>31,8; 56,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,28; 46,28</t>
+          <t>32,17; 46,55</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,91</t>
+          <t>0,0; 84,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,62</t>
+          <t>0,0; 48,34</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>39,18%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>27,44; 36,14</t>
+          <t>27,22; 35,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,51; 28,94</t>
+          <t>19,38; 28,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33,63; 44,64</t>
+          <t>33,49; 44,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28,56; 39,63</t>
+          <t>30,58; 41,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,95; 36,97</t>
+          <t>25,12; 37,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,64; 41,25</t>
+          <t>27,66; 41,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,33; 47,98</t>
+          <t>34,78; 48,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>28,62; 45,46</t>
+          <t>37,93; 47,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27,74; 35,08</t>
+          <t>27,72; 34,98</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24,0; 32,52</t>
+          <t>24,38; 32,36</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35,78; 44,41</t>
+          <t>35,89; 44,44</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,31; 40,89</t>
+          <t>35,34; 42,83</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>12016</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10531; 24112</t>
+          <t>11133; 24019</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1365; 7856</t>
+          <t>1432; 7942</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4013; 11974</t>
+          <t>3267; 11745</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5989</t>
+          <t>0; 9218</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2879; 10744</t>
+          <t>2806; 9960</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1142; 7983</t>
+          <t>1012; 8004</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2920; 9092</t>
+          <t>2901; 9070</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1759; 11517</t>
+          <t>2016; 12320</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16120; 31458</t>
+          <t>15646; 31706</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4428; 13762</t>
+          <t>4356; 13731</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8215; 18709</t>
+          <t>7443; 18589</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2958; 14266</t>
+          <t>5451; 19187</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24957</t>
+          <t>32058</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20871</t>
+          <t>21317</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>45828</t>
+          <t>53375</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37940; 61199</t>
+          <t>37702; 62866</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14765; 32573</t>
+          <t>14334; 31686</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20969; 39175</t>
+          <t>20966; 40208</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15249; 35159</t>
+          <t>20753; 43370</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14305; 30374</t>
+          <t>13498; 29438</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17135; 33515</t>
+          <t>15813; 32284</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9367; 21385</t>
+          <t>9765; 21832</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14093; 28624</t>
+          <t>14269; 28683</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57574; 86257</t>
+          <t>56775; 85816</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34720; 59900</t>
+          <t>35016; 57995</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34641; 58169</t>
+          <t>35566; 57262</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34124; 59243</t>
+          <t>39966; 67012</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26635</t>
+          <t>30191</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28746</t>
+          <t>32586</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55381</t>
+          <t>62777</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35337; 57580</t>
+          <t>34056; 56278</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18901; 36683</t>
+          <t>19103; 37189</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31471; 52214</t>
+          <t>30978; 52345</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18472; 36281</t>
+          <t>20480; 41480</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14657; 29860</t>
+          <t>15001; 29422</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18726; 35560</t>
+          <t>18645; 35630</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23053; 39679</t>
+          <t>22620; 38884</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21931; 36180</t>
+          <t>24948; 41183</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>53462; 80792</t>
+          <t>53680; 80656</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42461; 68048</t>
+          <t>42291; 67940</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60430; 87109</t>
+          <t>60766; 88006</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44899; 67759</t>
+          <t>50516; 75297</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39382</t>
+          <t>45945</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>56683</t>
+          <t>56790</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96066</t>
+          <t>102735</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20769; 40384</t>
+          <t>20481; 40972</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10359; 25488</t>
+          <t>10723; 26553</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27023; 46358</t>
+          <t>26634; 46503</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29645; 49398</t>
+          <t>35363; 57205</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9126; 20292</t>
+          <t>9100; 20938</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4328; 15278</t>
+          <t>5111; 16440</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15909; 31532</t>
+          <t>15908; 30776</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27211; 76648</t>
+          <t>47920; 66107</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32991; 55732</t>
+          <t>32714; 56254</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18260; 38016</t>
+          <t>18854; 38505</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>48042; 72779</t>
+          <t>47565; 72990</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>64103; 116658</t>
+          <t>89543; 117569</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22406</t>
+          <t>24418</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24801</t>
+          <t>28394</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47208</t>
+          <t>52811</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3780; 13684</t>
+          <t>3597; 13847</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2015; 10546</t>
+          <t>2000; 10507</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13154; 26412</t>
+          <t>13186; 26950</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15701; 29923</t>
+          <t>17004; 32006</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1021; 7988</t>
+          <t>1020; 7974</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5898; 15691</t>
+          <t>5411; 15889</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8318; 20257</t>
+          <t>7827; 19946</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19505; 30100</t>
+          <t>22825; 34892</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6725; 18865</t>
+          <t>6815; 18823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9518; 23935</t>
+          <t>8582; 23438</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24960; 42669</t>
+          <t>24053; 42798</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>38190; 56502</t>
+          <t>42739; 61842</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1024</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2358</t>
+          <t>0; 2529</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 2954</t>
+          <t>0; 3223</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>115185</t>
+          <t>137708</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>138214</t>
+          <t>147031</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>253399</t>
+          <t>284739</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>129613; 170683</t>
+          <t>128558; 169966</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>63279; 93865</t>
+          <t>62856; 92954</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>117715; 156230</t>
+          <t>117232; 155947</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>96204; 133498</t>
+          <t>116852; 160285</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>54919; 81376</t>
+          <t>55287; 82728</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>61476; 88549</t>
+          <t>59371; 88706</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>74264; 103788</t>
+          <t>75223; 104953</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>101182; 160700</t>
+          <t>130709; 162433</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>192104; 242897</t>
+          <t>191958; 242244</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>129351; 175264</t>
+          <t>131419; 174395</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>202638; 251475</t>
+          <t>203259; 251646</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>209245; 282302</t>
+          <t>256828; 311246</t>
         </is>
       </c>
     </row>
